--- a/VerveStacks_CHN_grids_kan10/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_CHN_grids_kan10/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN_grids_kan10\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C7DAE152-6429-444F-A5D2-0D9A7854A588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{97970FA9-5EAE-4706-9AAC-698386C537E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2573" yWindow="2573" windowWidth="21600" windowHeight="12682" xr2:uid="{D7BAE86E-EB77-4235-A7D3-A6F34CD8A070}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{B48EC014-6E42-49A4-AC12-BF03068A7410}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -589,7 +589,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9605CCC8-0F3F-4AAD-AB95-B6B8CBCD92EC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7736FDF0-2924-4009-9DB6-D8D78BB39DE5}">
   <dimension ref="B3:L22"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_CHN_grids_kan10/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_CHN_grids_kan10/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN_grids_kan10\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{97970FA9-5EAE-4706-9AAC-698386C537E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D58C8F7C-E533-4353-B131-4CB7D75DFC78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{B48EC014-6E42-49A4-AC12-BF03068A7410}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{63B42214-480C-4AAC-865A-F8B1E9DB3B6E}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -589,7 +589,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7736FDF0-2924-4009-9DB6-D8D78BB39DE5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9DD5011-6FC3-46A8-BFD2-08BFD9137448}">
   <dimension ref="B3:L22"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_CHN_grids_kan10/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_CHN_grids_kan10/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN_grids_kan10\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D58C8F7C-E533-4353-B131-4CB7D75DFC78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0C8C86D7-D809-480B-8AF2-ABE26A164058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{63B42214-480C-4AAC-865A-F8B1E9DB3B6E}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{3890B98A-E500-4748-8C44-EEF1AD0BF5EC}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -30,6 +30,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
     </ext>
   </extLst>
 </workbook>
@@ -589,7 +592,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9DD5011-6FC3-46A8-BFD2-08BFD9137448}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E95B692-13D0-4E11-890B-C42074818065}">
   <dimension ref="B3:L22"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
